--- a/AAII_Financials/Quarterly/DNUT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DNUT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
   <si>
     <t>DNUT</t>
   </si>
@@ -656,372 +656,385 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="25" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E7" s="2">
         <v>46110</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46019</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45928</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45837</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45746</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45655</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45564</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45200</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45109</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45018</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44927</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44836</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44745</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44654</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44563</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44472</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44381</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44290</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44199</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44101</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44010</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43919</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43828</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>331000</v>
+      </c>
+      <c r="E8" s="3">
         <v>367000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>392400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>375300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>379800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>375200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>404000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>379900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>438800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>442700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>450900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>407400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>408900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>419000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>404600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>377500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>375200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>372500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>370600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>342800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>349200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>321800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>325600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>290200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>245000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>261200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>265300</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>244900</v>
+      </c>
+      <c r="E9" s="3">
         <v>276400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>286500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>292200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>303300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>289600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>298700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>287900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>320400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>312200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>313900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>296700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>297600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>301600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>269800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>259900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>252700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>243000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>324900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>228300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>221500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>207200</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB9" s="3">
         <v>172400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>183100</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>86100</v>
+      </c>
+      <c r="E10" s="3">
         <v>90600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>105800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>83100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>76400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>85600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>105400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>92000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>118500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>130500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>137000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>110600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>111300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>117300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>134800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>117600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>122500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>129500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>45700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>114500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>127700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>114600</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB10" s="3">
         <v>72600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>78100</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1051,8 +1064,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1134,8 +1148,11 @@
       <c r="AC12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1217,77 +1234,80 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E14" s="3">
         <v>1900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>13300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-4500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>418400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-92700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>25100</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
         <v>2700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>500</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="3">
         <v>-1700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1300,91 +1320,97 @@
       <c r="AC14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E15" s="3">
         <v>32100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>33900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>33400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>35800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>33900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>34000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>31400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>34600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>33600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>36800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>32000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>29200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>27900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>26500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>28100</v>
-      </c>
-      <c r="S15" s="3">
-        <v>27800</v>
       </c>
       <c r="T15" s="3">
         <v>27800</v>
       </c>
       <c r="U15" s="3">
+        <v>27800</v>
+      </c>
+      <c r="V15" s="3">
         <v>27400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>25700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>25200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>23400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>22800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>20400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>18100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>19100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>19600</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1411,174 +1437,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>337700</v>
+      </c>
+      <c r="E17" s="3">
         <v>377700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>386300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>387000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>407400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>395300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>413100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>401500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>431700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>430800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>430600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>409500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>400500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>400700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>399400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>378500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>367700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>355200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>354100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>341000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>338400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>308100</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AA17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB17" s="3">
         <v>245500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>256800</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-10600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>6100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-11700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-27600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-20100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-9100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-21600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>20300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>18300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>17300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>16500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>10800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>13700</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4400</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1608,218 +1641,225 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-9000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-10700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-10000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-7800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-6600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-9300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-7600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-12900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-7200</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E21" s="3">
         <v>30500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>39800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>22400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>14200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>24200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>10200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>40700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>44900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>56300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>28900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>36500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>45200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>21000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>17100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>27500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>38500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>34600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>19900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>23100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>29900</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB21" s="3">
         <v>30400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>12500</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E22" s="3">
         <v>15600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>16500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>16400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>16700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>16200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>15600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>16300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>14500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>13700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>14000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>12800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>12100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>12000</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>500</v>
       </c>
       <c r="R22" s="3">
         <v>500</v>
@@ -1828,203 +1868,212 @@
         <v>500</v>
       </c>
       <c r="T22" s="3">
+        <v>500</v>
+      </c>
+      <c r="U22" s="3">
         <v>400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>3000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>6200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>5800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>5600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>6400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>5800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-19100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-24000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-22900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-461600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-36100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-24500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>55300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-19600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-15900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-11500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>10300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-13300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-13000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-13200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-12400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-9300</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E24" s="3">
         <v>3600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-2800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-20500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-2700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-2400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>17700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-3600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-21500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>24400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-7600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-5100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-2300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>9900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>11500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>11400</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2106,174 +2155,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-19800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-22700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-29100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-20100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-441100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-33400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-22200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>37600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-40300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-11800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>6500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-15000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-400</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AA26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB26" s="3">
         <v>-11700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-10900</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-28200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-32100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-19400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-435300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-37600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-22400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>39600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-8500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-40500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-13100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-17100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AA27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB27" s="3">
         <v>-12600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-11500</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2355,8 +2413,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2438,8 +2499,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2521,8 +2585,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2604,174 +2671,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>300</v>
+      </c>
+      <c r="E32" s="3">
         <v>9000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>10700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>10000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>7800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>6600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>9300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>7600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>12900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>7200</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB32" s="3">
         <v>6200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>11000</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-22800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-27800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-19400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-435300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-33300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-22400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>39600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-8500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-40500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-13100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-17100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AA33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB33" s="3">
         <v>-12600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-11500</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2853,179 +2929,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-22800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-27800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-19400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-435300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-33300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-22400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>39600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-8500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-40500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-13100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-17100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AA35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB35" s="3">
         <v>-12600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-11500</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E38" s="2">
         <v>46110</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46019</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45928</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45837</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45746</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45655</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45564</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45200</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45109</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45018</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44927</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44836</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44745</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44654</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44563</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44472</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44381</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44290</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44199</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44101</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44010</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43919</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43828</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3055,8 +3140,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3086,77 +3172,78 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E41" s="3">
         <v>74200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>42400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>30700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>21300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>18700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>29000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>25400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>28600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>33100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>38200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>25700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>26600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>29700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>35400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>28100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>25800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>31600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>38600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>44900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>37400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>50700</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>5</v>
       </c>
@@ -3169,8 +3256,11 @@
       <c r="AC41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3190,32 +3280,32 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>100</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>1000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>200</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -3229,17 +3319,17 @@
         <v>0</v>
       </c>
       <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
         <v>600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>900</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z42" s="3" t="s">
         <v>5</v>
       </c>
@@ -3252,77 +3342,80 @@
       <c r="AC42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>91600</v>
+      </c>
+      <c r="E43" s="3">
         <v>64400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>72500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>73500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>75300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>86200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>83900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>81400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>75500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>75700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>74900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>67700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>66700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>68000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>69400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>63500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>59600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>56400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>62200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>60100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>49200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>67000</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>5</v>
       </c>
@@ -3335,77 +3428,80 @@
       <c r="AC43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E44" s="3">
         <v>27200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>26900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>28100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>33700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>31500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>28100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>31500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>39500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>39300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>34700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>35100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>34000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>36400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>46200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>49400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>47400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>41000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>34900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>36100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>38500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>38000</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z44" s="3" t="s">
         <v>5</v>
       </c>
@@ -3418,77 +3514,80 @@
       <c r="AC44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E45" s="3">
         <v>2100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>100</v>
       </c>
       <c r="H45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="I45" s="3">
+        <v>100</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O45" s="3">
         <v>900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>27300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>33500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>29700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>20600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>21300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>22300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>21000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>14600</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>5</v>
       </c>
@@ -3501,77 +3600,80 @@
       <c r="AC45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>165400</v>
+      </c>
+      <c r="E46" s="3">
         <v>186900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>174500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>161800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>154600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>158000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>172900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>164300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>168200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>174000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>173600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>160100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>159300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>155600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>178300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>174500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>162500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>149700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>156900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>164000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>146800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>171000</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>5</v>
       </c>
@@ -3584,49 +3686,52 @@
       <c r="AC46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E47" s="3">
         <v>22100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>7400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>90800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>91300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>91000</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N47" s="3">
         <v>2800</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3667,77 +3772,80 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>725700</v>
+      </c>
+      <c r="E48" s="3">
         <v>720700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>856500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>901400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>928000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>955100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>921000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>899200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1007500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>999900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>995200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>966100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>935500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>908900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>889700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>861000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>863100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>874900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>874100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>838200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>829400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>820600</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3750,77 +3858,80 @@
       <c r="AC48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1397500</v>
+      </c>
+      <c r="E49" s="3">
         <v>1402400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1510000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1512000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1524100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1866500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1867500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1892100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2024000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2037700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2048300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2041500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2059500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2057400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2054000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2040600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2052500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2090700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2097800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2083400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2099300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2107500</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>5</v>
       </c>
@@ -3833,8 +3944,11 @@
       <c r="AC49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3916,8 +4030,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3999,77 +4116,80 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>52800</v>
+      </c>
+      <c r="E52" s="3">
         <v>54500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>43700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>18000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>17700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>19000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>17200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>18400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>23800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>22700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>18600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>19600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>19800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>22900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>26500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>25800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>21800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>18000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>16400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>17200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>18000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>17600</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>5</v>
       </c>
@@ -4082,8 +4202,11 @@
       <c r="AC52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4165,77 +4288,80 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2363300</v>
+      </c>
+      <c r="E54" s="3">
         <v>2386600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2593000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2599800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2630500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3089300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3072000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3065100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3223500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3234300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3240600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3187200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3174100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3144800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3148500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3101900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3099900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3133300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3145300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3102700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3093600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3116700</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>5</v>
       </c>
@@ -4248,8 +4374,11 @@
       <c r="AC54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4279,8 +4408,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4310,77 +4440,78 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>148500</v>
+      </c>
+      <c r="E57" s="3">
         <v>130700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>134400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>116500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>97400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>117200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>123300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>123100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>135200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>128600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>156500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>178700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>216400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>205200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>328900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>311400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>323100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>303400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>298500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>279700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>296300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>298300</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>5</v>
       </c>
@@ -4393,77 +4524,80 @@
       <c r="AC57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>118400</v>
+      </c>
+      <c r="E58" s="3">
         <v>105200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>120900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>124400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>117600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>107400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>103000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>97100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>115000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>110600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>105000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>92900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>83700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>80200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>40000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>40200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>39800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>36700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>36600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>38600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>539000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>37600</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>5</v>
       </c>
@@ -4476,77 +4610,80 @@
       <c r="AC58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>122000</v>
+      </c>
+      <c r="E59" s="3">
         <v>106100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>122600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>122400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>151400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>128000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>152900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>153500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>150100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>156200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>152600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>107600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>68900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>96900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>147600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>157400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>154400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>155200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>191100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>175300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>212600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>164000</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4559,77 +4696,80 @@
       <c r="AC59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>465100</v>
+      </c>
+      <c r="E60" s="3">
         <v>446000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>457300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>448900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>457600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>449500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>486200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>475500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>493600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>490100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>525600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>525000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>446700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>446000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>516500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>509000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>517300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>495200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>526200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>493600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1047900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>499900</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>5</v>
       </c>
@@ -4642,77 +4782,80 @@
       <c r="AC60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1145500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1172600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1312400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1321700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1314000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1349000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1249900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1221100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1348900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1336000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1291200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1269200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1253600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1209000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>739100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>738500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>686000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>680700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>680300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>682700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>626400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1167000</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -4725,77 +4868,80 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E62" s="3">
         <v>27500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>40300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>33200</v>
-      </c>
-      <c r="G62" s="3">
-        <v>31600</v>
       </c>
       <c r="H62" s="3">
         <v>31600</v>
       </c>
       <c r="I62" s="3">
+        <v>31600</v>
+      </c>
+      <c r="J62" s="3">
         <v>32200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>31500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>27500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>29400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>30100</v>
-      </c>
-      <c r="N62" s="3">
-        <v>28500</v>
       </c>
       <c r="O62" s="3">
         <v>28500</v>
       </c>
       <c r="P62" s="3">
+        <v>28500</v>
+      </c>
+      <c r="Q62" s="3">
         <v>35900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>594100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>580600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>587600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>601900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>603100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>606600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>597500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>586400</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>5</v>
       </c>
@@ -4808,8 +4954,11 @@
       <c r="AC62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4891,8 +5040,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4974,8 +5126,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5057,77 +5212,80 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1743500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1753300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1916000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1906000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1912300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1957900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1907600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1856000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1994200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1986400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1976800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1938200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1867900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1837700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1952200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1928400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1893000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1883100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1913700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1875100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2365200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2429500</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>5</v>
       </c>
@@ -5140,8 +5298,11 @@
       <c r="AC66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5171,8 +5332,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5254,8 +5416,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5337,8 +5502,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5420,8 +5588,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5503,77 +5674,80 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-864500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-844200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-821400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-793600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-774200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-338900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-299600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-271200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-304800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-293400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-279000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-275700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-229300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-223700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-217500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-208900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-190000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-180300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-178400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-173900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-633600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-145300</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>5</v>
       </c>
@@ -5586,8 +5760,11 @@
       <c r="AC72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5669,8 +5846,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5752,8 +5932,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5835,77 +6018,80 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>618100</v>
+      </c>
+      <c r="E76" s="3">
         <v>631800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>650100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>670300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>693600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1101600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1134500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1179700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1135300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1153200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1169700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1152100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1208500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1203900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1196300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1173400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1206900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1250100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1231600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1227600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>728300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>687200</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>5</v>
       </c>
@@ -5918,8 +6104,11 @@
       <c r="AC76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6001,179 +6190,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E80" s="2">
         <v>46110</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46019</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45928</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45837</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45746</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45655</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45564</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45200</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45109</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45018</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44927</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44836</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44745</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44654</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44563</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44472</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44381</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44290</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44199</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44101</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44010</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43919</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43828</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-22800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-27800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-19400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-435300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-33300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-22400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>39600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-8500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-40500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-13100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-17100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AA81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB81" s="3">
         <v>-12600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-11500</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6203,91 +6401,95 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E83" s="3">
         <v>26200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>26300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>23600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>27200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>26200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>29400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>24600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>21800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>20700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>19300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>21000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>20800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>20600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>26500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>28100</v>
-      </c>
-      <c r="S83" s="3">
-        <v>27800</v>
       </c>
       <c r="T83" s="3">
         <v>27800</v>
       </c>
       <c r="U83" s="3">
+        <v>27800</v>
+      </c>
+      <c r="V83" s="3">
         <v>27400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>25700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>25200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>23400</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AA83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB83" s="3">
         <v>37200</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6369,8 +6571,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6452,8 +6657,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6535,8 +6743,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6618,8 +6829,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6701,91 +6915,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E89" s="3">
         <v>20200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>45000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>42300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-32500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-20800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>27000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>33200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-17700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>35900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>10400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>69100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>16800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>25500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>28400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>42400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>41900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>16200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>40600</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AA89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB89" s="3">
         <v>13900</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6815,91 +7035,95 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-17100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-26700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-28200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-25900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-33900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-26100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-31700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-29100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-32800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-34300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-27700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-36700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-23500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-22000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-29500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-36000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-30600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-22500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-30300</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-44100</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6981,8 +7205,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7064,91 +7291,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-32100</v>
+      </c>
+      <c r="E94" s="3">
         <v>100100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-15600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-27500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>56700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-25800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-25500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>109900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-36100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-29000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-34200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-34300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-27700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-33800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-39400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-21800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-26400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-36700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-30500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-22600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-63700</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AA94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-40700</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7178,28 +7411,29 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
         <v>6000</v>
       </c>
       <c r="I96" s="3">
-        <v>5900</v>
+        <v>6000</v>
       </c>
       <c r="J96" s="3">
         <v>5900</v>
@@ -7223,7 +7457,7 @@
         <v>5900</v>
       </c>
       <c r="Q96" s="3">
-        <v>-5900</v>
+        <v>5900</v>
       </c>
       <c r="R96" s="3">
         <v>-5900</v>
@@ -7235,7 +7469,7 @@
         <v>-5900</v>
       </c>
       <c r="U96" s="3">
-        <v>0</v>
+        <v>-5900</v>
       </c>
       <c r="V96" s="3">
         <v>0</v>
@@ -7261,8 +7495,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7344,8 +7581,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7427,8 +7667,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7510,253 +7753,265 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-88100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-20200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-20600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>36800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-117600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>43600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>44300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>35400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-9700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-31100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>28400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-7500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-6600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-11300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-3200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-6300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>36800</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AA100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB100" s="3">
         <v>215300</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3500</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-2200</v>
       </c>
       <c r="P101" s="3">
         <v>-2200</v>
       </c>
       <c r="Q101" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="R101" s="3">
         <v>3000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3500</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-2200</v>
       </c>
       <c r="T101" s="3">
         <v>-2200</v>
       </c>
       <c r="U101" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="V101" s="3">
         <v>-400</v>
-      </c>
-      <c r="V101" s="3">
-        <v>-700</v>
       </c>
       <c r="W101" s="3">
         <v>-700</v>
       </c>
       <c r="X101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-500</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AA101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB101" s="3">
         <v>200</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-52600</v>
+      </c>
+      <c r="E102" s="3">
         <v>31800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>11700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>9300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-10100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>12500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>7200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-6900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-5900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>7600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-13300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>13300</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AA102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB102" s="3">
         <v>188700</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
